--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -19005,7 +19005,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 20:53:30</t>
+          <t>2026-10-01 21:18:35</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>aa2b944</t>
+          <t>49adde6</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -853,7 +853,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1011,31 +1011,23 @@
           <t>06-009</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1306,31 +1298,23 @@
           <t>06-016</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr"/>
+      <c r="K20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1377,7 +1361,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1453,31 +1437,23 @@
           <t>06-019</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
-        </is>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1502,23 +1478,31 @@
           <t>06-020</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J24" s="7" t="inlineStr"/>
-      <c r="K24" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1543,23 +1527,31 @@
           <t>06-021</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1584,23 +1576,31 @@
           <t>06-022</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr"/>
-      <c r="K26" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2871,23 +2871,31 @@
           <t>06-053</t>
         </is>
       </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr"/>
-      <c r="K57" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -2945,23 +2953,31 @@
           <t>06-055</t>
         </is>
       </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr"/>
-      <c r="K59" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -2982,23 +2998,31 @@
           <t>06-056</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr"/>
-      <c r="K60" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -3093,23 +3117,31 @@
           <t>06-059</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr"/>
-      <c r="K63" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -3130,23 +3162,31 @@
           <t>06-060</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -4799,23 +4839,31 @@
           <t>06-105</t>
         </is>
       </c>
-      <c r="G109" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J109" s="7" t="inlineStr"/>
-      <c r="K109" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K109" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -4840,23 +4888,31 @@
           <t>06-106</t>
         </is>
       </c>
-      <c r="G110" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H110" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J110" s="7" t="inlineStr"/>
-      <c r="K110" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K110" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -4881,23 +4937,31 @@
           <t>06-107</t>
         </is>
       </c>
-      <c r="G111" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H111" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J111" s="7" t="inlineStr"/>
-      <c r="K111" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K111" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -4922,23 +4986,31 @@
           <t>06-108</t>
         </is>
       </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J112" s="7" t="inlineStr"/>
-      <c r="K112" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J112" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K112" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -4963,23 +5035,31 @@
           <t>06-109</t>
         </is>
       </c>
-      <c r="G113" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J113" s="7" t="inlineStr"/>
-      <c r="K113" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K113" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -6990,7 +7070,7 @@
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7320,31 +7400,23 @@
           <t>06-009</t>
         </is>
       </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
-        </is>
-      </c>
-      <c r="T10" s="7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -7916,31 +7988,23 @@
           <t>06-016</t>
         </is>
       </c>
-      <c r="P17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="Q17" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr"/>
+      <c r="T17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -8030,7 +8094,7 @@
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -8192,31 +8256,23 @@
           <t>06-019</t>
         </is>
       </c>
-      <c r="P20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -8284,23 +8340,31 @@
           <t>06-020</t>
         </is>
       </c>
-      <c r="P21" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q21" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R21" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr"/>
-      <c r="T21" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -8368,23 +8432,31 @@
           <t>06-021</t>
         </is>
       </c>
-      <c r="P22" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q22" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr"/>
-      <c r="T22" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -8452,23 +8524,31 @@
           <t>06-022</t>
         </is>
       </c>
-      <c r="P23" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q23" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R23" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr"/>
-      <c r="T23" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -8978,7 +9058,7 @@
       </c>
       <c r="T29" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9146,7 @@
       </c>
       <c r="T30" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10322,7 @@
       </c>
       <c r="T44" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10414,7 @@
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -11072,23 +11152,31 @@
           <t>06-053</t>
         </is>
       </c>
-      <c r="P54" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q54" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R54" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr"/>
-      <c r="T54" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T54" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -11232,23 +11320,31 @@
           <t>06-055</t>
         </is>
       </c>
-      <c r="P56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R56" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr"/>
-      <c r="T56" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T56" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -11312,23 +11408,31 @@
           <t>06-056</t>
         </is>
       </c>
-      <c r="P57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr"/>
-      <c r="T57" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -11552,23 +11656,31 @@
           <t>06-059</t>
         </is>
       </c>
-      <c r="P60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr"/>
-      <c r="T60" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T60" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -11632,23 +11744,31 @@
           <t>06-060</t>
         </is>
       </c>
-      <c r="P61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R61" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr"/>
-      <c r="T61" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T61" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -15236,23 +15356,31 @@
           <t>06-105</t>
         </is>
       </c>
-      <c r="P106" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q106" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P106" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q106" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S106" s="7" t="inlineStr"/>
-      <c r="T106" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S106" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T106" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -15320,23 +15448,31 @@
           <t>06-106</t>
         </is>
       </c>
-      <c r="P107" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q107" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P107" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q107" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S107" s="7" t="inlineStr"/>
-      <c r="T107" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S107" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T107" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -15404,23 +15540,31 @@
           <t>06-107</t>
         </is>
       </c>
-      <c r="P108" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q108" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P108" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q108" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S108" s="7" t="inlineStr"/>
-      <c r="T108" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S108" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T108" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -15488,23 +15632,31 @@
           <t>06-108</t>
         </is>
       </c>
-      <c r="P109" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q109" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P109" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q109" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S109" s="7" t="inlineStr"/>
-      <c r="T109" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S109" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T109" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -15572,23 +15724,31 @@
           <t>06-109</t>
         </is>
       </c>
-      <c r="P110" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q110" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P110" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q110" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S110" s="7" t="inlineStr"/>
-      <c r="T110" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S110" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T110" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -19005,7 +19165,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 21:18:35</t>
+          <t>2026-10-01 22:59:51</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19177,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>49adde6</t>
+          <t>e04913e</t>
         </is>
       </c>
     </row>
@@ -19439,26 +19599,22 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -19682,26 +19838,22 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -19793,26 +19945,22 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>✗</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
-        </is>
-      </c>
+          <t>Specified</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -19830,22 +19978,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -19863,22 +20015,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -19896,22 +20052,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -20955,22 +21115,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
@@ -21021,22 +21185,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
@@ -21054,22 +21222,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
@@ -21153,22 +21325,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
@@ -21186,22 +21362,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
@@ -22242,22 +22422,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
@@ -22275,22 +22459,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D104" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
@@ -22308,22 +22496,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D105" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E105" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D105" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
@@ -22341,22 +22533,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E106" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
@@ -22374,22 +22570,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D107" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E107" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -3020,7 +3020,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -11430,7 +11430,7 @@
       </c>
       <c r="T57" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="T60" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="T61" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -19165,7 +19165,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01 22:59:51</t>
+          <t>2026-10-02 10:31:41</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>e04913e</t>
+          <t>80489b0</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -19165,7 +19165,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:31:41</t>
+          <t>2026-10-02 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19177,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80489b0</t>
+          <t>e20d5f2</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -1011,23 +1011,31 @@
           <t>06-009</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1298,23 +1306,31 @@
           <t>06-016</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr"/>
-      <c r="K20" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1437,23 +1453,31 @@
           <t>06-019</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr"/>
-      <c r="K23" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1748,23 +1772,31 @@
           <t>06-026</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1965,23 +1997,31 @@
           <t>06-031</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -2002,23 +2042,31 @@
           <t>06-032</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -2752,23 +2800,31 @@
           <t>06-050</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J54" s="7" t="inlineStr"/>
-      <c r="K54" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -2793,23 +2849,31 @@
           <t>06-051</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J55" s="7" t="inlineStr"/>
-      <c r="K55" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3392,23 +3456,31 @@
           <t>06-066</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J70" s="7" t="inlineStr"/>
-      <c r="K70" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -3429,23 +3501,31 @@
           <t>06-067</t>
         </is>
       </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J71" s="7" t="inlineStr"/>
-      <c r="K71" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -3466,23 +3546,31 @@
           <t>06-068</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="inlineStr"/>
-      <c r="K72" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -3577,23 +3665,31 @@
           <t>06-071</t>
         </is>
       </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -3614,23 +3710,31 @@
           <t>06-072</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr"/>
-      <c r="K76" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -3873,23 +3977,31 @@
           <t>06-079</t>
         </is>
       </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J83" s="7" t="inlineStr"/>
-      <c r="K83" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -3947,23 +4059,31 @@
           <t>06-081</t>
         </is>
       </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J85" s="7" t="inlineStr"/>
-      <c r="K85" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K85" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -3984,23 +4104,31 @@
           <t>06-082</t>
         </is>
       </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="inlineStr"/>
-      <c r="K86" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K86" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -4095,23 +4223,31 @@
           <t>06-085</t>
         </is>
       </c>
-      <c r="G89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J89" s="7" t="inlineStr"/>
-      <c r="K89" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K89" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -4132,23 +4268,31 @@
           <t>06-086</t>
         </is>
       </c>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="inlineStr"/>
-      <c r="K90" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K90" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -5556,23 +5700,31 @@
           <t>06-122</t>
         </is>
       </c>
-      <c r="G126" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H126" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J126" s="7" t="inlineStr"/>
-      <c r="K126" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K126" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -5630,23 +5782,31 @@
           <t>06-124</t>
         </is>
       </c>
-      <c r="G128" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H128" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J128" s="7" t="inlineStr"/>
-      <c r="K128" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K128" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -7400,23 +7560,31 @@
           <t>06-009</t>
         </is>
       </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr"/>
-      <c r="T10" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -7988,23 +8156,31 @@
           <t>06-016</t>
         </is>
       </c>
-      <c r="P17" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q17" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr"/>
-      <c r="T17" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -8256,23 +8432,31 @@
           <t>06-019</t>
         </is>
       </c>
-      <c r="P20" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr"/>
-      <c r="T20" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -8868,23 +9052,31 @@
           <t>06-026</t>
         </is>
       </c>
-      <c r="P27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R27" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr"/>
-      <c r="T27" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T27" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -9300,23 +9492,31 @@
           <t>06-031</t>
         </is>
       </c>
-      <c r="P32" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q32" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R32" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr"/>
-      <c r="T32" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -9380,23 +9580,31 @@
           <t>06-032</t>
         </is>
       </c>
-      <c r="P33" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R33" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr"/>
-      <c r="T33" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -10904,23 +11112,31 @@
           <t>06-050</t>
         </is>
       </c>
-      <c r="P51" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q51" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr"/>
-      <c r="T51" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -10988,23 +11204,31 @@
           <t>06-051</t>
         </is>
       </c>
-      <c r="P52" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q52" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R52" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr"/>
-      <c r="T52" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -12232,23 +12456,31 @@
           <t>06-066</t>
         </is>
       </c>
-      <c r="P67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R67" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S67" s="7" t="inlineStr"/>
-      <c r="T67" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -12312,23 +12544,31 @@
           <t>06-067</t>
         </is>
       </c>
-      <c r="P68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S68" s="7" t="inlineStr"/>
-      <c r="T68" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -12392,23 +12632,31 @@
           <t>06-068</t>
         </is>
       </c>
-      <c r="P69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S69" s="7" t="inlineStr"/>
-      <c r="T69" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -12632,23 +12880,31 @@
           <t>06-071</t>
         </is>
       </c>
-      <c r="P72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S72" s="7" t="inlineStr"/>
-      <c r="T72" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T72" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -12712,23 +12968,31 @@
           <t>06-072</t>
         </is>
       </c>
-      <c r="P73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R73" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S73" s="7" t="inlineStr"/>
-      <c r="T73" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T73" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -13272,23 +13536,31 @@
           <t>06-079</t>
         </is>
       </c>
-      <c r="P80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S80" s="7" t="inlineStr"/>
-      <c r="T80" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T80" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -13432,23 +13704,31 @@
           <t>06-081</t>
         </is>
       </c>
-      <c r="P82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S82" s="7" t="inlineStr"/>
-      <c r="T82" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T82" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -13512,23 +13792,31 @@
           <t>06-082</t>
         </is>
       </c>
-      <c r="P83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S83" s="7" t="inlineStr"/>
-      <c r="T83" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S83" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T83" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -13752,23 +14040,31 @@
           <t>06-085</t>
         </is>
       </c>
-      <c r="P86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S86" s="7" t="inlineStr"/>
-      <c r="T86" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T86" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -13832,23 +14128,31 @@
           <t>06-086</t>
         </is>
       </c>
-      <c r="P87" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q87" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S87" s="7" t="inlineStr"/>
-      <c r="T87" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S87" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T87" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -16804,23 +17108,31 @@
           <t>06-122</t>
         </is>
       </c>
-      <c r="P123" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q123" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P123" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q123" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S123" s="7" t="inlineStr"/>
-      <c r="T123" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S123" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T123" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -16964,23 +17276,31 @@
           <t>06-124</t>
         </is>
       </c>
-      <c r="P125" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q125" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P125" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q125" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S125" s="7" t="inlineStr"/>
-      <c r="T125" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S125" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T125" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -19165,7 +19485,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:41:41</t>
+          <t>2026-10-02 10:43:55</t>
         </is>
       </c>
     </row>
@@ -19177,7 +19497,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>e20d5f2</t>
+          <t>153705e</t>
         </is>
       </c>
     </row>
@@ -19599,22 +19919,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -19838,22 +20162,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -19945,22 +20273,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -20188,22 +20520,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -20369,22 +20705,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -20402,22 +20742,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -21016,22 +21360,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
@@ -21049,22 +21397,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
@@ -21564,22 +21916,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
@@ -21597,22 +21953,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G78" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
@@ -21630,22 +21990,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
@@ -21729,22 +22093,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G82" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
@@ -21762,22 +22130,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
@@ -21993,22 +22365,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
@@ -22059,22 +22435,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
@@ -22092,22 +22472,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
@@ -22191,22 +22575,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D96" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
@@ -22224,22 +22612,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D97" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
@@ -23003,22 +23395,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D120" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
@@ -23069,22 +23465,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -19485,7 +19485,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:43:55</t>
+          <t>2026-10-02 10:47:50</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>153705e</t>
+          <t>c955892</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -1056,23 +1056,31 @@
           <t>06-010</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="K14" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1093,23 +1101,31 @@
           <t>06-011</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1130,23 +1146,31 @@
           <t>06-012</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
-      <c r="K16" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1167,23 +1191,31 @@
           <t>06-013</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1649,23 +1681,31 @@
           <t>06-023</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr"/>
-      <c r="K27" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1690,23 +1730,31 @@
           <t>06-024</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr"/>
-      <c r="K28" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1731,23 +1779,31 @@
           <t>06-025</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J29" s="7" t="inlineStr"/>
-      <c r="K29" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1974,7 +2030,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2087,23 +2143,31 @@
           <t>06-033</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr"/>
-      <c r="K37" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -2124,23 +2188,31 @@
           <t>06-034</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2161,23 +2233,31 @@
           <t>06-035</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -2198,23 +2278,31 @@
           <t>06-036</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -2235,23 +2323,31 @@
           <t>06-037</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -2272,23 +2368,31 @@
           <t>06-038</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -2309,23 +2413,31 @@
           <t>06-039</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J43" s="7" t="inlineStr"/>
-      <c r="K43" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K43" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -2372,7 +2484,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2533,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2582,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2680,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2595,23 +2707,31 @@
           <t>06-045</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr"/>
-      <c r="K49" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K49" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -2636,23 +2756,31 @@
           <t>06-046</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J50" s="7" t="inlineStr"/>
-      <c r="K50" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K50" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -2677,23 +2805,31 @@
           <t>06-047</t>
         </is>
       </c>
-      <c r="G51" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr"/>
-      <c r="K51" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -2718,23 +2854,31 @@
           <t>06-048</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J52" s="7" t="inlineStr"/>
-      <c r="K52" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -2759,23 +2903,31 @@
           <t>06-049</t>
         </is>
       </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr"/>
-      <c r="K53" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K53" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -2898,23 +3050,31 @@
           <t>06-052</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J56" s="7" t="inlineStr"/>
-      <c r="K56" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2980,23 +3140,31 @@
           <t>06-054</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H58" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr"/>
-      <c r="K58" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -3107,23 +3275,31 @@
           <t>06-057</t>
         </is>
       </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H61" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J61" s="7" t="inlineStr"/>
-      <c r="K61" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -3144,23 +3320,31 @@
           <t>06-058</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr"/>
-      <c r="K62" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K62" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -3271,23 +3455,31 @@
           <t>06-061</t>
         </is>
       </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J65" s="7" t="inlineStr"/>
-      <c r="K65" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -3308,23 +3500,31 @@
           <t>06-062</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J66" s="7" t="inlineStr"/>
-      <c r="K66" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -3345,23 +3545,31 @@
           <t>06-063</t>
         </is>
       </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H67" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J67" s="7" t="inlineStr"/>
-      <c r="K67" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -3382,23 +3590,31 @@
           <t>06-064</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -3419,23 +3635,31 @@
           <t>06-065</t>
         </is>
       </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J69" s="7" t="inlineStr"/>
-      <c r="K69" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -3591,23 +3815,31 @@
           <t>06-069</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J73" s="7" t="inlineStr"/>
-      <c r="K73" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -3628,23 +3860,31 @@
           <t>06-070</t>
         </is>
       </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="inlineStr"/>
-      <c r="K74" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -3755,23 +3995,31 @@
           <t>06-073</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J77" s="7" t="inlineStr"/>
-      <c r="K77" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -3792,23 +4040,31 @@
           <t>06-074</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J78" s="7" t="inlineStr"/>
-      <c r="K78" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3829,23 +4085,31 @@
           <t>06-075</t>
         </is>
       </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J79" s="7" t="inlineStr"/>
-      <c r="K79" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -3866,23 +4130,31 @@
           <t>06-076</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J80" s="7" t="inlineStr"/>
-      <c r="K80" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K80" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -3903,23 +4175,31 @@
           <t>06-077</t>
         </is>
       </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr"/>
-      <c r="K81" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -3940,23 +4220,31 @@
           <t>06-078</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J82" s="7" t="inlineStr"/>
-      <c r="K82" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K82" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -4022,23 +4310,31 @@
           <t>06-080</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J84" s="7" t="inlineStr"/>
-      <c r="K84" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K84" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -4149,23 +4445,31 @@
           <t>06-083</t>
         </is>
       </c>
-      <c r="G87" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H87" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="inlineStr"/>
-      <c r="K87" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -4186,23 +4490,31 @@
           <t>06-084</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J88" s="7" t="inlineStr"/>
-      <c r="K88" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K88" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -4313,23 +4625,31 @@
           <t>06-087</t>
         </is>
       </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="inlineStr"/>
-      <c r="K91" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K91" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -4350,23 +4670,31 @@
           <t>06-088</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J92" s="7" t="inlineStr"/>
-      <c r="K92" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -4387,23 +4715,31 @@
           <t>06-089</t>
         </is>
       </c>
-      <c r="G93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr"/>
-      <c r="K93" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -4424,23 +4760,31 @@
           <t>06-090</t>
         </is>
       </c>
-      <c r="G94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr"/>
-      <c r="K94" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K94" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -4461,23 +4805,31 @@
           <t>06-091</t>
         </is>
       </c>
-      <c r="G95" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H95" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G95" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="inlineStr"/>
-      <c r="K95" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K95" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -5152,7 +5504,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5228,23 +5580,31 @@
           <t>06-110</t>
         </is>
       </c>
-      <c r="G114" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J114" s="7" t="inlineStr"/>
-      <c r="K114" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K114" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -5269,23 +5629,31 @@
           <t>06-111</t>
         </is>
       </c>
-      <c r="G115" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J115" s="7" t="inlineStr"/>
-      <c r="K115" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K115" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -5310,23 +5678,31 @@
           <t>06-112</t>
         </is>
       </c>
-      <c r="G116" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H116" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J116" s="7" t="inlineStr"/>
-      <c r="K116" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K116" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -5351,23 +5727,31 @@
           <t>06-113</t>
         </is>
       </c>
-      <c r="G117" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I117" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J117" s="7" t="inlineStr"/>
-      <c r="K117" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K117" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -5392,23 +5776,31 @@
           <t>06-114</t>
         </is>
       </c>
-      <c r="G118" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J118" s="7" t="inlineStr"/>
-      <c r="K118" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K118" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -5433,23 +5825,31 @@
           <t>06-115</t>
         </is>
       </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J119" s="7" t="inlineStr"/>
-      <c r="K119" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K119" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -5474,23 +5874,31 @@
           <t>06-116</t>
         </is>
       </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H120" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G120" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J120" s="7" t="inlineStr"/>
-      <c r="K120" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K120" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -5515,23 +5923,31 @@
           <t>06-117</t>
         </is>
       </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G121" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J121" s="7" t="inlineStr"/>
-      <c r="K121" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="K121" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -5552,23 +5968,31 @@
           <t>06-118</t>
         </is>
       </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H122" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J122" s="7" t="inlineStr"/>
-      <c r="K122" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K122" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -5589,23 +6013,31 @@
           <t>06-119</t>
         </is>
       </c>
-      <c r="G123" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J123" s="7" t="inlineStr"/>
-      <c r="K123" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -5626,23 +6058,31 @@
           <t>06-120</t>
         </is>
       </c>
-      <c r="G124" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J124" s="7" t="inlineStr"/>
-      <c r="K124" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K124" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -5663,23 +6103,31 @@
           <t>06-121</t>
         </is>
       </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H125" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J125" s="7" t="inlineStr"/>
-      <c r="K125" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="K125" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -5745,23 +6193,31 @@
           <t>06-123</t>
         </is>
       </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H127" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J127" s="7" t="inlineStr"/>
-      <c r="K127" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K127" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -5804,7 +6260,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5864,23 +6320,31 @@
           <t>06-126</t>
         </is>
       </c>
-      <c r="G130" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H130" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I130" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J130" s="7" t="inlineStr"/>
-      <c r="K130" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -5901,23 +6365,31 @@
           <t>06-127</t>
         </is>
       </c>
-      <c r="G131" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H131" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I131" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J131" s="7" t="inlineStr"/>
-      <c r="K131" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -5938,23 +6410,31 @@
           <t>06-128</t>
         </is>
       </c>
-      <c r="G132" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H132" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G132" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I132" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J132" s="7" t="inlineStr"/>
-      <c r="K132" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -5975,23 +6455,31 @@
           <t>06-129</t>
         </is>
       </c>
-      <c r="G133" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H133" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G133" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I133" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J133" s="7" t="inlineStr"/>
-      <c r="K133" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -6012,23 +6500,31 @@
           <t>06-130</t>
         </is>
       </c>
-      <c r="G134" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H134" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I134" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J134" s="7" t="inlineStr"/>
-      <c r="K134" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -7648,23 +8144,31 @@
           <t>06-010</t>
         </is>
       </c>
-      <c r="P11" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R11" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr"/>
-      <c r="T11" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -7728,23 +8232,31 @@
           <t>06-011</t>
         </is>
       </c>
-      <c r="P12" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q12" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R12" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr"/>
-      <c r="T12" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7808,23 +8320,31 @@
           <t>06-012</t>
         </is>
       </c>
-      <c r="P13" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr"/>
-      <c r="T13" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7888,23 +8408,31 @@
           <t>06-013</t>
         </is>
       </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr"/>
-      <c r="T14" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -8800,23 +9328,31 @@
           <t>06-023</t>
         </is>
       </c>
-      <c r="P24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R24" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr"/>
-      <c r="T24" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -8884,23 +9420,31 @@
           <t>06-024</t>
         </is>
       </c>
-      <c r="P25" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R25" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr"/>
-      <c r="T25" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -8968,23 +9512,31 @@
           <t>06-025</t>
         </is>
       </c>
-      <c r="P26" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q26" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R26" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr"/>
-      <c r="T26" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -9426,7 +9978,7 @@
       </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -9668,23 +10220,31 @@
           <t>06-033</t>
         </is>
       </c>
-      <c r="P34" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q34" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R34" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr"/>
-      <c r="T34" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T34" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -9748,23 +10308,31 @@
           <t>06-034</t>
         </is>
       </c>
-      <c r="P35" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q35" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R35" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr"/>
-      <c r="T35" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T35" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -9828,23 +10396,31 @@
           <t>06-035</t>
         </is>
       </c>
-      <c r="P36" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q36" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R36" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr"/>
-      <c r="T36" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T36" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -9908,23 +10484,31 @@
           <t>06-036</t>
         </is>
       </c>
-      <c r="P37" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q37" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R37" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr"/>
-      <c r="T37" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T37" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -9988,23 +10572,31 @@
           <t>06-037</t>
         </is>
       </c>
-      <c r="P38" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q38" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R38" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr"/>
-      <c r="T38" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T38" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -10068,23 +10660,31 @@
           <t>06-038</t>
         </is>
       </c>
-      <c r="P39" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q39" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R39" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr"/>
-      <c r="T39" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T39" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -10148,23 +10748,31 @@
           <t>06-039</t>
         </is>
       </c>
-      <c r="P40" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q40" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R40" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr"/>
-      <c r="T40" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T40" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -10254,7 +10862,7 @@
       </c>
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10954,7 @@
       </c>
       <c r="T42" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10438,7 +11046,7 @@
       </c>
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10622,7 +11230,7 @@
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -10692,23 +11300,31 @@
           <t>06-045</t>
         </is>
       </c>
-      <c r="P46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr"/>
-      <c r="T46" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T46" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -10776,23 +11392,31 @@
           <t>06-046</t>
         </is>
       </c>
-      <c r="P47" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q47" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R47" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr"/>
-      <c r="T47" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T47" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -10860,23 +11484,31 @@
           <t>06-047</t>
         </is>
       </c>
-      <c r="P48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R48" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr"/>
-      <c r="T48" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T48" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -10944,23 +11576,31 @@
           <t>06-048</t>
         </is>
       </c>
-      <c r="P49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr"/>
-      <c r="T49" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T49" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -11028,23 +11668,31 @@
           <t>06-049</t>
         </is>
       </c>
-      <c r="P50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R50" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr"/>
-      <c r="T50" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T50" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -11296,23 +11944,31 @@
           <t>06-052</t>
         </is>
       </c>
-      <c r="P53" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q53" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R53" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr"/>
-      <c r="T53" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T53" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -11464,23 +12120,31 @@
           <t>06-054</t>
         </is>
       </c>
-      <c r="P55" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q55" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R55" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr"/>
-      <c r="T55" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T55" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -11720,23 +12384,31 @@
           <t>06-057</t>
         </is>
       </c>
-      <c r="P58" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q58" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr"/>
-      <c r="T58" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T58" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -11800,23 +12472,31 @@
           <t>06-058</t>
         </is>
       </c>
-      <c r="P59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R59" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr"/>
-      <c r="T59" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T59" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -12056,23 +12736,31 @@
           <t>06-061</t>
         </is>
       </c>
-      <c r="P62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q62" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R62" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr"/>
-      <c r="T62" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T62" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -12136,23 +12824,31 @@
           <t>06-062</t>
         </is>
       </c>
-      <c r="P63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R63" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr"/>
-      <c r="T63" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T63" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -12216,23 +12912,31 @@
           <t>06-063</t>
         </is>
       </c>
-      <c r="P64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q64" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr"/>
-      <c r="T64" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T64" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -12296,23 +13000,31 @@
           <t>06-064</t>
         </is>
       </c>
-      <c r="P65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R65" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S65" s="7" t="inlineStr"/>
-      <c r="T65" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T65" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -12376,23 +13088,31 @@
           <t>06-065</t>
         </is>
       </c>
-      <c r="P66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q66" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S66" s="7" t="inlineStr"/>
-      <c r="T66" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
+      <c r="T66" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -12720,23 +13440,31 @@
           <t>06-069</t>
         </is>
       </c>
-      <c r="P70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q70" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S70" s="7" t="inlineStr"/>
-      <c r="T70" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T70" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -12800,23 +13528,31 @@
           <t>06-070</t>
         </is>
       </c>
-      <c r="P71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q71" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S71" s="7" t="inlineStr"/>
-      <c r="T71" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S71" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T71" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -13056,23 +13792,31 @@
           <t>06-073</t>
         </is>
       </c>
-      <c r="P74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S74" s="7" t="inlineStr"/>
-      <c r="T74" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T74" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -13136,23 +13880,31 @@
           <t>06-074</t>
         </is>
       </c>
-      <c r="P75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S75" s="7" t="inlineStr"/>
-      <c r="T75" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S75" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T75" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -13216,23 +13968,31 @@
           <t>06-075</t>
         </is>
       </c>
-      <c r="P76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S76" s="7" t="inlineStr"/>
-      <c r="T76" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T76" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -13296,23 +14056,31 @@
           <t>06-076</t>
         </is>
       </c>
-      <c r="P77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q77" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S77" s="7" t="inlineStr"/>
-      <c r="T77" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T77" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -13376,23 +14144,31 @@
           <t>06-077</t>
         </is>
       </c>
-      <c r="P78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q78" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S78" s="7" t="inlineStr"/>
-      <c r="T78" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S78" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T78" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -13456,23 +14232,31 @@
           <t>06-078</t>
         </is>
       </c>
-      <c r="P79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q79" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S79" s="7" t="inlineStr"/>
-      <c r="T79" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S79" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T79" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -13624,23 +14408,31 @@
           <t>06-080</t>
         </is>
       </c>
-      <c r="P81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S81" s="7" t="inlineStr"/>
-      <c r="T81" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T81" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -13880,23 +14672,31 @@
           <t>06-083</t>
         </is>
       </c>
-      <c r="P84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S84" s="7" t="inlineStr"/>
-      <c r="T84" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T84" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -13960,23 +14760,31 @@
           <t>06-084</t>
         </is>
       </c>
-      <c r="P85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S85" s="7" t="inlineStr"/>
-      <c r="T85" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S85" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T85" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -14216,23 +15024,31 @@
           <t>06-087</t>
         </is>
       </c>
-      <c r="P88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S88" s="7" t="inlineStr"/>
-      <c r="T88" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T88" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -14296,23 +15112,31 @@
           <t>06-088</t>
         </is>
       </c>
-      <c r="P89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S89" s="7" t="inlineStr"/>
-      <c r="T89" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T89" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -14376,23 +15200,31 @@
           <t>06-089</t>
         </is>
       </c>
-      <c r="P90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q90" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S90" s="7" t="inlineStr"/>
-      <c r="T90" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T90" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -14456,23 +15288,31 @@
           <t>06-090</t>
         </is>
       </c>
-      <c r="P91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S91" s="7" t="inlineStr"/>
-      <c r="T91" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T91" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -14536,23 +15376,31 @@
           <t>06-091</t>
         </is>
       </c>
-      <c r="P92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q92" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q92" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S92" s="7" t="inlineStr"/>
-      <c r="T92" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S92" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T92" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -15958,7 +16806,7 @@
       </c>
       <c r="T109" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -16120,23 +16968,31 @@
           <t>06-110</t>
         </is>
       </c>
-      <c r="P111" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q111" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P111" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q111" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S111" s="7" t="inlineStr"/>
-      <c r="T111" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S111" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T111" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -16204,23 +17060,31 @@
           <t>06-111</t>
         </is>
       </c>
-      <c r="P112" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q112" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P112" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q112" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S112" s="7" t="inlineStr"/>
-      <c r="T112" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S112" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T112" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -16288,23 +17152,31 @@
           <t>06-112</t>
         </is>
       </c>
-      <c r="P113" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q113" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P113" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q113" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S113" s="7" t="inlineStr"/>
-      <c r="T113" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S113" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T113" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -16372,23 +17244,31 @@
           <t>06-113</t>
         </is>
       </c>
-      <c r="P114" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q114" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P114" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q114" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S114" s="7" t="inlineStr"/>
-      <c r="T114" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S114" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T114" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -16456,23 +17336,31 @@
           <t>06-114</t>
         </is>
       </c>
-      <c r="P115" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q115" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P115" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q115" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S115" s="7" t="inlineStr"/>
-      <c r="T115" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S115" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T115" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -16540,23 +17428,31 @@
           <t>06-115</t>
         </is>
       </c>
-      <c r="P116" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q116" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P116" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q116" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S116" s="7" t="inlineStr"/>
-      <c r="T116" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S116" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T116" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -16624,23 +17520,31 @@
           <t>06-116</t>
         </is>
       </c>
-      <c r="P117" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q117" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P117" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q117" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S117" s="7" t="inlineStr"/>
-      <c r="T117" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S117" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T117" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -16708,23 +17612,31 @@
           <t>06-117</t>
         </is>
       </c>
-      <c r="P118" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q118" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P118" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q118" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S118" s="7" t="inlineStr"/>
-      <c r="T118" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S118" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
+      <c r="T118" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -16788,23 +17700,31 @@
           <t>06-118</t>
         </is>
       </c>
-      <c r="P119" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q119" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P119" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q119" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S119" s="7" t="inlineStr"/>
-      <c r="T119" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S119" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T119" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -16868,23 +17788,31 @@
           <t>06-119</t>
         </is>
       </c>
-      <c r="P120" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q120" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P120" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q120" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S120" s="7" t="inlineStr"/>
-      <c r="T120" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S120" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
+      <c r="T120" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -16948,23 +17876,31 @@
           <t>06-120</t>
         </is>
       </c>
-      <c r="P121" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q121" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P121" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q121" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S121" s="7" t="inlineStr"/>
-      <c r="T121" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S121" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T121" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -17028,23 +17964,31 @@
           <t>06-121</t>
         </is>
       </c>
-      <c r="P122" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q122" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P122" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q122" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S122" s="7" t="inlineStr"/>
-      <c r="T122" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S122" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
+      <c r="T122" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -17196,23 +18140,31 @@
           <t>06-123</t>
         </is>
       </c>
-      <c r="P124" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q124" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P124" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q124" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S124" s="7" t="inlineStr"/>
-      <c r="T124" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S124" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T124" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -17298,7 +18250,7 @@
       </c>
       <c r="T125" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -17444,23 +18396,31 @@
           <t>06-126</t>
         </is>
       </c>
-      <c r="P127" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q127" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P127" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q127" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S127" s="7" t="inlineStr"/>
-      <c r="T127" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S127" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T127" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -17524,23 +18484,31 @@
           <t>06-127</t>
         </is>
       </c>
-      <c r="P128" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q128" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P128" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q128" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S128" s="7" t="inlineStr"/>
-      <c r="T128" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S128" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T128" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -17604,23 +18572,31 @@
           <t>06-128</t>
         </is>
       </c>
-      <c r="P129" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q129" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P129" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q129" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S129" s="7" t="inlineStr"/>
-      <c r="T129" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S129" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T129" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -17684,23 +18660,31 @@
           <t>06-129</t>
         </is>
       </c>
-      <c r="P130" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q130" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P130" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q130" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R130" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S130" s="7" t="inlineStr"/>
-      <c r="T130" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S130" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T130" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -17764,23 +18748,31 @@
           <t>06-130</t>
         </is>
       </c>
-      <c r="P131" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q131" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P131" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q131" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R131" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S131" s="7" t="inlineStr"/>
-      <c r="T131" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S131" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T131" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -19485,7 +20477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:47:50</t>
+          <t>2026-10-02 11:47:39</t>
         </is>
       </c>
     </row>
@@ -19497,7 +20489,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c955892</t>
+          <t>14aeca4</t>
         </is>
       </c>
     </row>
@@ -19956,22 +20948,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -19989,22 +20985,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -20022,22 +21022,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -20055,22 +21059,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -20421,22 +21429,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -20454,22 +21466,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -20487,22 +21503,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/wal_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -20779,22 +21799,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -20812,22 +21836,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
@@ -20845,22 +21873,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
@@ -20878,22 +21910,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
@@ -20911,22 +21947,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
@@ -20944,22 +21984,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
@@ -20977,22 +22021,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
@@ -21195,22 +22243,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
@@ -21228,22 +22280,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
@@ -21261,22 +22317,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
@@ -21294,22 +22354,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
@@ -21327,22 +22391,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
@@ -21434,22 +22502,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
@@ -21504,22 +22576,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
@@ -21611,22 +22687,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
@@ -21644,22 +22724,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
@@ -21751,22 +22835,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
@@ -21784,22 +22872,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
@@ -21817,22 +22909,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
@@ -21850,22 +22946,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
@@ -21883,22 +22983,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/compaction_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
@@ -22027,22 +23131,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G80" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -22060,22 +23168,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
@@ -22167,22 +23279,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G84" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
@@ -22200,22 +23316,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
@@ -22233,22 +23353,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
@@ -22266,22 +23390,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D87" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
@@ -22299,22 +23427,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
@@ -22332,22 +23464,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E89" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
@@ -22402,22 +23538,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
@@ -22509,22 +23649,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
@@ -22542,22 +23686,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D95" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
@@ -22649,22 +23797,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/memtable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
@@ -22682,22 +23834,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
@@ -22715,22 +23871,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D100" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
@@ -22748,22 +23908,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E101" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
@@ -22781,22 +23945,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D102" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
@@ -22999,22 +24167,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E108" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D108" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
@@ -23032,22 +24204,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E109" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
@@ -23065,22 +24241,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E110" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
@@ -23098,22 +24278,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E111" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
@@ -23131,22 +24315,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
@@ -23164,22 +24352,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E113" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
@@ -23197,22 +24389,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E114" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
@@ -23230,22 +24426,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D115" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E115" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/manifest_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
@@ -23263,22 +24463,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G116" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
@@ -23296,22 +24500,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E117" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/engine_api_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
@@ -23329,22 +24537,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E118" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D118" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
@@ -23362,22 +24574,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/sstable_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
@@ -23432,22 +24648,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
@@ -23535,22 +24755,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E124" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
@@ -23568,22 +24792,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
@@ -23601,22 +24829,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E126" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
@@ -23634,22 +24866,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E127" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
@@ -23667,22 +24903,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D128" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E128" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D128" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E128" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -20477,7 +20477,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 11:47:39</t>
+          <t>2026-10-02 12:00:31</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14aeca4</t>
+          <t>5168869</t>
         </is>
       </c>
     </row>

--- a/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
+++ b/evidence/workbooks/06_LSM_KV_ENGINE_ULTIMATE_145_Master_STATUS.xlsx
@@ -4850,23 +4850,31 @@
           <t>06-092</t>
         </is>
       </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H96" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J96" s="7" t="inlineStr"/>
-      <c r="K96" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K96" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -4887,23 +4895,31 @@
           <t>06-093</t>
         </is>
       </c>
-      <c r="G97" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H97" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="inlineStr"/>
-      <c r="K97" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K97" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -4924,23 +4940,31 @@
           <t>06-094</t>
         </is>
       </c>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H98" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G98" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr"/>
-      <c r="K98" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K98" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -4961,23 +4985,31 @@
           <t>06-095</t>
         </is>
       </c>
-      <c r="G99" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H99" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J99" s="7" t="inlineStr"/>
-      <c r="K99" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K99" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -4998,23 +5030,31 @@
           <t>06-096</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H100" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="inlineStr"/>
-      <c r="K100" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -5035,23 +5075,31 @@
           <t>06-097</t>
         </is>
       </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H101" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr"/>
-      <c r="K101" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K101" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -5072,23 +5120,31 @@
           <t>06-098</t>
         </is>
       </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H102" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J102" s="7" t="inlineStr"/>
-      <c r="K102" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K102" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -5109,23 +5165,31 @@
           <t>06-099</t>
         </is>
       </c>
-      <c r="G103" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H103" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J103" s="7" t="inlineStr"/>
-      <c r="K103" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K103" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -5146,23 +5210,31 @@
           <t>06-100</t>
         </is>
       </c>
-      <c r="G104" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H104" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J104" s="7" t="inlineStr"/>
-      <c r="K104" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J104" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K104" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -5183,23 +5255,31 @@
           <t>06-101</t>
         </is>
       </c>
-      <c r="G105" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H105" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J105" s="7" t="inlineStr"/>
-      <c r="K105" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K105" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -5220,23 +5300,31 @@
           <t>06-102</t>
         </is>
       </c>
-      <c r="G106" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H106" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J106" s="7" t="inlineStr"/>
-      <c r="K106" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K106" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -5257,23 +5345,31 @@
           <t>06-103</t>
         </is>
       </c>
-      <c r="G107" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H107" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J107" s="7" t="inlineStr"/>
-      <c r="K107" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K107" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -5294,23 +5390,31 @@
           <t>06-104</t>
         </is>
       </c>
-      <c r="G108" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H108" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J108" s="7" t="inlineStr"/>
-      <c r="K108" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K108" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -6283,23 +6387,31 @@
           <t>06-125</t>
         </is>
       </c>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H129" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I129" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J129" s="7" t="inlineStr"/>
-      <c r="K129" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="K129" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -6631,23 +6743,31 @@
           <t>06-133</t>
         </is>
       </c>
-      <c r="G137" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H137" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J137" s="7" t="inlineStr"/>
-      <c r="K137" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -6795,23 +6915,31 @@
           <t>06-137</t>
         </is>
       </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H141" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I141" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J141" s="7" t="inlineStr"/>
-      <c r="K141" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -7057,23 +7185,31 @@
           <t>06-143</t>
         </is>
       </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="H147" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="I147" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="J147" s="7" t="inlineStr"/>
-      <c r="K147" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="K147" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -15464,23 +15600,31 @@
           <t>06-092</t>
         </is>
       </c>
-      <c r="P93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q93" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S93" s="7" t="inlineStr"/>
-      <c r="T93" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S93" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T93" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -15544,23 +15688,31 @@
           <t>06-093</t>
         </is>
       </c>
-      <c r="P94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q94" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S94" s="7" t="inlineStr"/>
-      <c r="T94" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S94" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T94" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -15624,23 +15776,31 @@
           <t>06-094</t>
         </is>
       </c>
-      <c r="P95" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q95" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P95" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q95" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S95" s="7" t="inlineStr"/>
-      <c r="T95" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S95" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T95" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -15704,23 +15864,31 @@
           <t>06-095</t>
         </is>
       </c>
-      <c r="P96" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q96" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P96" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q96" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S96" s="7" t="inlineStr"/>
-      <c r="T96" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S96" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T96" s="7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -15784,23 +15952,31 @@
           <t>06-096</t>
         </is>
       </c>
-      <c r="P97" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q97" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P97" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q97" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S97" s="7" t="inlineStr"/>
-      <c r="T97" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S97" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T97" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -15864,23 +16040,31 @@
           <t>06-097</t>
         </is>
       </c>
-      <c r="P98" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q98" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P98" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q98" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S98" s="7" t="inlineStr"/>
-      <c r="T98" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S98" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T98" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -15944,23 +16128,31 @@
           <t>06-098</t>
         </is>
       </c>
-      <c r="P99" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q99" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P99" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q99" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S99" s="7" t="inlineStr"/>
-      <c r="T99" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S99" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T99" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -16024,23 +16216,31 @@
           <t>06-099</t>
         </is>
       </c>
-      <c r="P100" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q100" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P100" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q100" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S100" s="7" t="inlineStr"/>
-      <c r="T100" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S100" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T100" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -16104,23 +16304,31 @@
           <t>06-100</t>
         </is>
       </c>
-      <c r="P101" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q101" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P101" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q101" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S101" s="7" t="inlineStr"/>
-      <c r="T101" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S101" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T101" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -16184,23 +16392,31 @@
           <t>06-101</t>
         </is>
       </c>
-      <c r="P102" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q102" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P102" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q102" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S102" s="7" t="inlineStr"/>
-      <c r="T102" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S102" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T102" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -16264,23 +16480,31 @@
           <t>06-102</t>
         </is>
       </c>
-      <c r="P103" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q103" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P103" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q103" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S103" s="7" t="inlineStr"/>
-      <c r="T103" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S103" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T103" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -16344,23 +16568,31 @@
           <t>06-103</t>
         </is>
       </c>
-      <c r="P104" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q104" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P104" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q104" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S104" s="7" t="inlineStr"/>
-      <c r="T104" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S104" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T104" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -16424,23 +16656,31 @@
           <t>06-104</t>
         </is>
       </c>
-      <c r="P105" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q105" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P105" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q105" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S105" s="7" t="inlineStr"/>
-      <c r="T105" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S105" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T105" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -18316,23 +18556,31 @@
           <t>06-125</t>
         </is>
       </c>
-      <c r="P126" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q126" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P126" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q126" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S126" s="7" t="inlineStr"/>
-      <c r="T126" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S126" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
+      <c r="T126" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -19008,23 +19256,31 @@
           <t>06-133</t>
         </is>
       </c>
-      <c r="P134" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q134" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P134" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q134" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R134" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S134" s="7" t="inlineStr"/>
-      <c r="T134" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S134" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T134" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -19344,23 +19600,31 @@
           <t>06-137</t>
         </is>
       </c>
-      <c r="P138" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q138" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P138" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q138" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R138" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S138" s="7" t="inlineStr"/>
-      <c r="T138" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S138" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T138" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -19864,23 +20128,31 @@
           <t>06-143</t>
         </is>
       </c>
-      <c r="P144" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="Q144" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="P144" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q144" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="R144" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="S144" s="7" t="inlineStr"/>
-      <c r="T144" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="S144" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/cache_memory_p1_tests.rs</t>
+        </is>
+      </c>
+      <c r="T144" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -20477,7 +20749,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 12:00:31</t>
+          <t>2026-10-02 20:05:03</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20761,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5168869</t>
+          <t>2700149</t>
         </is>
       </c>
     </row>
@@ -24722,22 +24994,26 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>✗</t>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Specified</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr"/>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>projects/06-lsm-kv-engine/backend/tests/security_tests.rs</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
